--- a/Results/Convex_combination/Clustering/n10000/Summary_Statistics.xlsx
+++ b/Results/Convex_combination/Clustering/n10000/Summary_Statistics.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,97 +362,142 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>H_Shannon_mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>H_Shannon_mean</t>
+          <t>H_Shannon_sd</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>H_Shannon_sd</t>
+          <t>H_Renyi_mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>H_Renyi_sd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>H_Tsallis_mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>H_Tsallis_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>H_Fisher_mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>H_Fisher_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>C_Shannon_mean</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>C_Shannon_sd</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>H_Renyi_mean</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>H_Renyi_sd</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>C_Renyi_mean</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>C_Renyi_sd</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>H_Tsallis_mean</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>H_Tsallis_sd</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>C_Tsallis_mean</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>C_Tsallis_sd</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>H_Fisher_mean</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>H_Fisher_sd</t>
+          <t>C_Fisher_mean</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>C_Fisher_mean</t>
+          <t>C_Fisher_sd</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>C_Fisher_sd</t>
+          <t>Disequilibrium_mean</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Disequilibrium_mean</t>
+          <t>Disequilibrium_sd</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Disequilibrium_sd</t>
+          <t>Var_H_Shannon_mean</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Shannon_sd</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Renyi_mean</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Renyi_sd</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Tsallis_mean</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Tsallis_sd</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Fisher_mean</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Var_H_Fisher_sd</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Var_C_Shannon_mean</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Var_C_Shannon_sd</t>
         </is>
       </c>
     </row>
@@ -463,61 +508,88 @@
         </is>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>0.7944818878465337</v>
       </c>
       <c r="C2">
-        <v>0.7944818878465337</v>
+        <v>0.004972723821586534</v>
       </c>
       <c r="D2">
-        <v>0.004972723821586534</v>
+        <v>0.7439035113256293</v>
       </c>
       <c r="E2">
+        <v>0.004824755276134653</v>
+      </c>
+      <c r="F2">
+        <v>0.8711807451185792</v>
+      </c>
+      <c r="G2">
+        <v>0.002960776115189072</v>
+      </c>
+      <c r="H2">
+        <v>3.037134550891914</v>
+      </c>
+      <c r="I2">
+        <v>0.09656957190226856</v>
+      </c>
+      <c r="J2">
         <v>0.2174276617336838</v>
       </c>
-      <c r="F2">
+      <c r="K2">
         <v>0.004395418436306179</v>
       </c>
-      <c r="G2">
-        <v>0.7439035113256293</v>
-      </c>
-      <c r="H2">
-        <v>0.004824755276134653</v>
-      </c>
-      <c r="I2">
+      <c r="L2">
         <v>0.1778941411946301</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>0.003590768260442677</v>
       </c>
-      <c r="K2">
-        <v>0.8711807451185792</v>
-      </c>
-      <c r="L2">
-        <v>0.002960776115189072</v>
-      </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.2083469457266104</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.004829255319801952</v>
       </c>
-      <c r="O2">
-        <v>3.037134550891914</v>
-      </c>
       <c r="P2">
-        <v>0.09656957190226856</v>
+        <v>0.7269919312034587</v>
       </c>
       <c r="Q2">
-        <v>0.7269919312034587</v>
+        <v>0.04249838541531036</v>
       </c>
       <c r="R2">
-        <v>0.04249838541531036</v>
+        <v>0.273716523027738</v>
       </c>
       <c r="S2">
-        <v>0.273716523027738</v>
+        <v>0.007257016941146823</v>
       </c>
       <c r="T2">
-        <v>0.007257016941146823</v>
+        <v>0.1921487826042637</v>
+      </c>
+      <c r="U2">
+        <v>0.01001768965353665</v>
+      </c>
+      <c r="V2">
+        <v>0.04497083984663459</v>
+      </c>
+      <c r="W2">
+        <v>0.003953271733285743</v>
+      </c>
+      <c r="X2">
+        <v>0.07127523229224519</v>
+      </c>
+      <c r="Y2">
+        <v>0.007151758209490461</v>
+      </c>
+      <c r="Z2">
+        <v>71.58674054706015</v>
+      </c>
+      <c r="AA2">
+        <v>2.550641840998153</v>
+      </c>
+      <c r="AB2">
+        <v>0.1370730671872683</v>
+      </c>
+      <c r="AC2">
+        <v>0.007618338032630846</v>
       </c>
     </row>
     <row r="3">
@@ -527,61 +599,88 @@
         </is>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>0.8441408810038232</v>
       </c>
       <c r="C3">
-        <v>0.8441408810038232</v>
+        <v>0.005618172796590303</v>
       </c>
       <c r="D3">
-        <v>0.005618172796590303</v>
+        <v>0.7984669574248252</v>
       </c>
       <c r="E3">
+        <v>0.005921280999069127</v>
+      </c>
+      <c r="F3">
+        <v>0.9031746576796369</v>
+      </c>
+      <c r="G3">
+        <v>0.003323012834772537</v>
+      </c>
+      <c r="H3">
+        <v>2.472557651460757</v>
+      </c>
+      <c r="I3">
+        <v>0.09937714437055475</v>
+      </c>
+      <c r="J3">
         <v>0.1744451697251402</v>
       </c>
-      <c r="F3">
+      <c r="K3">
         <v>0.005598581633944756</v>
       </c>
-      <c r="G3">
-        <v>0.7984669574248252</v>
-      </c>
-      <c r="H3">
-        <v>0.005921280999069127</v>
-      </c>
-      <c r="I3">
+      <c r="L3">
         <v>0.1441797617430875</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>0.004526435204868891</v>
       </c>
-      <c r="K3">
-        <v>0.9031746576796369</v>
-      </c>
-      <c r="L3">
-        <v>0.003323012834772537</v>
-      </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.1631098454972973</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.005720481728166223</v>
       </c>
-      <c r="O3">
-        <v>2.472557651460757</v>
-      </c>
       <c r="P3">
-        <v>0.09937714437055475</v>
+        <v>0.4472574660849187</v>
       </c>
       <c r="Q3">
-        <v>0.4472574660849187</v>
+        <v>0.03494907707891034</v>
       </c>
       <c r="R3">
-        <v>0.03494907707891034</v>
+        <v>0.206706181076073</v>
       </c>
       <c r="S3">
-        <v>0.206706181076073</v>
+        <v>0.007999614080495009</v>
       </c>
       <c r="T3">
-        <v>0.007999614080495009</v>
+        <v>0.1980890393476299</v>
+      </c>
+      <c r="U3">
+        <v>0.009152439670738505</v>
+      </c>
+      <c r="V3">
+        <v>0.04487136592243415</v>
+      </c>
+      <c r="W3">
+        <v>0.002957204791974952</v>
+      </c>
+      <c r="X3">
+        <v>0.07085879642268757</v>
+      </c>
+      <c r="Y3">
+        <v>0.005288581697565774</v>
+      </c>
+      <c r="Z3">
+        <v>66.81693736716169</v>
+      </c>
+      <c r="AA3">
+        <v>2.943279553043202</v>
+      </c>
+      <c r="AB3">
+        <v>0.1892955659618927</v>
+      </c>
+      <c r="AC3">
+        <v>0.007999320014956613</v>
       </c>
     </row>
     <row r="4">
@@ -591,61 +690,88 @@
         </is>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>0.9767224280345115</v>
       </c>
       <c r="C4">
-        <v>0.9767224280345115</v>
+        <v>0.001614988793727402</v>
       </c>
       <c r="D4">
-        <v>0.001614988793727402</v>
+        <v>0.9662213255967462</v>
       </c>
       <c r="E4">
+        <v>0.002288947892536462</v>
+      </c>
+      <c r="F4">
+        <v>0.9858556060375154</v>
+      </c>
+      <c r="G4">
+        <v>0.0009846614002000187</v>
+      </c>
+      <c r="H4">
+        <v>0.2031243127751638</v>
+      </c>
+      <c r="I4">
+        <v>0.02141757103589466</v>
+      </c>
+      <c r="J4">
         <v>0.03016345706148782</v>
       </c>
-      <c r="F4">
+      <c r="K4">
         <v>0.002049939454211467</v>
       </c>
-      <c r="G4">
-        <v>0.9662213255967462</v>
-      </c>
-      <c r="H4">
-        <v>0.002288947892536462</v>
-      </c>
-      <c r="I4">
+      <c r="L4">
         <v>0.02607238153347338</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>0.001753303605513071</v>
       </c>
-      <c r="K4">
-        <v>0.9858556060375154</v>
-      </c>
-      <c r="L4">
-        <v>0.0009846614002000187</v>
-      </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.02660466750325549</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.001825705600650306</v>
       </c>
-      <c r="O4">
-        <v>0.2031243127751638</v>
-      </c>
       <c r="P4">
-        <v>0.02141757103589466</v>
+        <v>0.005516020029920301</v>
       </c>
       <c r="Q4">
-        <v>0.005516020029920301</v>
+        <v>0.0009401233178717317</v>
       </c>
       <c r="R4">
-        <v>0.0009401233178717317</v>
+        <v>0.03088580350349528</v>
       </c>
       <c r="S4">
-        <v>0.03088580350349528</v>
+        <v>0.00215048243683127</v>
       </c>
       <c r="T4">
-        <v>0.00215048243683127</v>
+        <v>0.0234406290126078</v>
+      </c>
+      <c r="U4">
+        <v>0.003919569911084816</v>
+      </c>
+      <c r="V4">
+        <v>0.005518383960660878</v>
+      </c>
+      <c r="W4">
+        <v>0.0008903767896433752</v>
+      </c>
+      <c r="X4">
+        <v>0.008602220772292994</v>
+      </c>
+      <c r="Y4">
+        <v>0.002711079245648806</v>
+      </c>
+      <c r="Z4">
+        <v>3.741394705908122</v>
+      </c>
+      <c r="AA4">
+        <v>0.4947423612864056</v>
+      </c>
+      <c r="AB4">
+        <v>0.03833144273664915</v>
+      </c>
+      <c r="AC4">
+        <v>0.006284637671453579</v>
       </c>
     </row>
     <row r="5">
@@ -655,60 +781,87 @@
         </is>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>0.5908799293792387</v>
       </c>
       <c r="C5">
-        <v>0.5908799293792387</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.580865963903443</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.7572529685318561</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>6.376743834386861</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
         <v>0.347240991307292</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0.580865963903443</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>0.2982790672206421</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0.7572529685318561</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>0.3888551286184345</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
-        <v>6.376743834386861</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.274506204570922</v>
       </c>
       <c r="Q5">
-        <v>3.274506204570922</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.5876676022353532</v>
       </c>
       <c r="S5">
-        <v>0.5876676022353532</v>
+        <v>0</v>
       </c>
       <c r="T5">
+        <v>0.003502220893870125</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>-0.006993442270825718</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0.006151896564890038</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>-0.00840919224086285</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.0001907271167832054</v>
+      </c>
+      <c r="AC5">
         <v>0</v>
       </c>
     </row>
@@ -719,60 +872,87 @@
         </is>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>0.3910776339782189</v>
       </c>
       <c r="C6">
-        <v>0.3910776339782189</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.3462651770119069</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0.5317158512868505</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3.628339195001781</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>0.284137796480921</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.3462651770119069</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>0.2198315108667727</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0.5317158512868505</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
       <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>0.3375675831710366</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
       <c r="O6">
-        <v>3.628339195001781</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.303504193108462</v>
       </c>
       <c r="Q6">
-        <v>2.303504193108462</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.7265508732640694</v>
       </c>
       <c r="S6">
-        <v>0.7265508732640694</v>
+        <v>0</v>
       </c>
       <c r="T6">
+        <v>0.07908149550595681</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0.06771322653535089</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.1066199031510572</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>7.404718280581235</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.01652238002097946</v>
+      </c>
+      <c r="AC6">
         <v>0</v>
       </c>
     </row>
@@ -783,61 +963,88 @@
         </is>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>0.4433662313490916</v>
       </c>
       <c r="C7">
-        <v>0.4433662313490916</v>
+        <v>0.005796336087793892</v>
       </c>
       <c r="D7">
-        <v>0.005796336087793892</v>
+        <v>0.3658834401553669</v>
       </c>
       <c r="E7">
+        <v>0.003181042924385274</v>
+      </c>
+      <c r="F7">
+        <v>0.5539521972147431</v>
+      </c>
+      <c r="G7">
+        <v>0.003551530833275082</v>
+      </c>
+      <c r="H7">
+        <v>2.813577176459131</v>
+      </c>
+      <c r="I7">
+        <v>0.06642518107114648</v>
+      </c>
+      <c r="J7">
         <v>0.2783170922741619</v>
       </c>
-      <c r="F7">
+      <c r="K7">
         <v>0.0004663156017755403</v>
       </c>
-      <c r="G7">
-        <v>0.3658834401553669</v>
-      </c>
-      <c r="H7">
-        <v>0.003181042924385274</v>
-      </c>
-      <c r="I7">
+      <c r="L7">
         <v>0.200707112856849</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>0.001224193595661112</v>
       </c>
-      <c r="K7">
-        <v>0.5539521972147431</v>
-      </c>
-      <c r="L7">
-        <v>0.003551530833275082</v>
-      </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.3038828899372524</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.002511337934419945</v>
       </c>
-      <c r="O7">
-        <v>2.813577176459131</v>
-      </c>
       <c r="P7">
-        <v>0.06642518107114648</v>
+        <v>1.544073721646477</v>
       </c>
       <c r="Q7">
-        <v>1.544073721646477</v>
+        <v>0.05809490763716704</v>
       </c>
       <c r="R7">
-        <v>0.05809490763716704</v>
+        <v>0.6278531135417441</v>
       </c>
       <c r="S7">
-        <v>0.6278531135417441</v>
+        <v>0.009133473020499903</v>
       </c>
       <c r="T7">
-        <v>0.009133473020499903</v>
+        <v>0.2076610790953174</v>
+      </c>
+      <c r="U7">
+        <v>0.01647300664666101</v>
+      </c>
+      <c r="V7">
+        <v>0.1049516086284012</v>
+      </c>
+      <c r="W7">
+        <v>0.01074594235585463</v>
+      </c>
+      <c r="X7">
+        <v>0.165683462113652</v>
+      </c>
+      <c r="Y7">
+        <v>0.01117925294545052</v>
+      </c>
+      <c r="Z7">
+        <v>17.32858731044854</v>
+      </c>
+      <c r="AA7">
+        <v>1.445334382446014</v>
+      </c>
+      <c r="AB7">
+        <v>0.009372440322686398</v>
+      </c>
+      <c r="AC7">
+        <v>0.0007038860435488718</v>
       </c>
     </row>
     <row r="8">
@@ -847,61 +1054,88 @@
         </is>
       </c>
       <c r="B8">
-        <v>50</v>
+        <v>0.5332070492323669</v>
       </c>
       <c r="C8">
-        <v>0.5332070492323669</v>
+        <v>0.01308951821763429</v>
       </c>
       <c r="D8">
-        <v>0.01308951821763429</v>
+        <v>0.4269797168269326</v>
       </c>
       <c r="E8">
+        <v>0.01026478687519261</v>
+      </c>
+      <c r="F8">
+        <v>0.6188746111170528</v>
+      </c>
+      <c r="G8">
+        <v>0.01040084684666018</v>
+      </c>
+      <c r="H8">
+        <v>2.017768717373423</v>
+      </c>
+      <c r="I8">
+        <v>0.08827033418810416</v>
+      </c>
+      <c r="J8">
         <v>0.2690965015844677</v>
       </c>
-      <c r="F8">
+      <c r="K8">
         <v>0.00201430682859187</v>
       </c>
-      <c r="G8">
-        <v>0.4269797168269326</v>
-      </c>
-      <c r="H8">
-        <v>0.01026478687519261</v>
-      </c>
-      <c r="I8">
+      <c r="L8">
         <v>0.1882966589325888</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>0.001561055969453872</v>
       </c>
-      <c r="K8">
-        <v>0.6188746111170528</v>
-      </c>
-      <c r="L8">
-        <v>0.01040084684666018</v>
-      </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.272983257516994</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.004172316562023845</v>
       </c>
-      <c r="O8">
-        <v>2.017768717373423</v>
-      </c>
       <c r="P8">
-        <v>0.08827033418810416</v>
+        <v>0.8916901258429473</v>
       </c>
       <c r="Q8">
-        <v>0.8916901258429473</v>
+        <v>0.06732174177100243</v>
       </c>
       <c r="R8">
-        <v>0.06732174177100243</v>
+        <v>0.505063536388268</v>
       </c>
       <c r="S8">
-        <v>0.505063536388268</v>
+        <v>0.01615407298275467</v>
       </c>
       <c r="T8">
-        <v>0.01615407298275467</v>
+        <v>0.4193906893807232</v>
+      </c>
+      <c r="U8">
+        <v>0.02305672569360686</v>
+      </c>
+      <c r="V8">
+        <v>0.2076208746055073</v>
+      </c>
+      <c r="W8">
+        <v>0.01547269747708014</v>
+      </c>
+      <c r="X8">
+        <v>0.3300048132597305</v>
+      </c>
+      <c r="Y8">
+        <v>0.02061248439586613</v>
+      </c>
+      <c r="Z8">
+        <v>14.34117085782104</v>
+      </c>
+      <c r="AA8">
+        <v>0.9508355975949571</v>
+      </c>
+      <c r="AB8">
+        <v>0.01113452608971342</v>
+      </c>
+      <c r="AC8">
+        <v>0.002871533019853966</v>
       </c>
     </row>
     <row r="9">
@@ -911,61 +1145,88 @@
         </is>
       </c>
       <c r="B9">
-        <v>50</v>
+        <v>0.6386694171505568</v>
       </c>
       <c r="C9">
-        <v>0.6386694171505568</v>
+        <v>0.01811872317724497</v>
       </c>
       <c r="D9">
-        <v>0.01811872317724497</v>
+        <v>0.5266091847064053</v>
       </c>
       <c r="E9">
+        <v>0.01977537421308335</v>
+      </c>
+      <c r="F9">
+        <v>0.7120382460216492</v>
+      </c>
+      <c r="G9">
+        <v>0.01716867976140488</v>
+      </c>
+      <c r="H9">
+        <v>1.630461826468364</v>
+      </c>
+      <c r="I9">
+        <v>0.0328005125735916</v>
+      </c>
+      <c r="J9">
         <v>0.2511850948374495</v>
       </c>
-      <c r="F9">
+      <c r="K9">
         <v>0.003549703365950419</v>
       </c>
-      <c r="G9">
-        <v>0.5266091847064053</v>
-      </c>
-      <c r="H9">
-        <v>0.01977537421308335</v>
-      </c>
-      <c r="I9">
+      <c r="L9">
         <v>0.1809073274074718</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>0.001046333038321472</v>
       </c>
-      <c r="K9">
-        <v>0.7120382460216492</v>
-      </c>
-      <c r="L9">
-        <v>0.01716867976140488</v>
-      </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.2447454307216</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.004533428535744368</v>
       </c>
-      <c r="O9">
-        <v>1.630461826468364</v>
-      </c>
       <c r="P9">
-        <v>0.0328005125735916</v>
+        <v>0.5613708034519127</v>
       </c>
       <c r="Q9">
-        <v>0.5613708034519127</v>
+        <v>0.03397062663556095</v>
       </c>
       <c r="R9">
-        <v>0.03397062663556095</v>
+        <v>0.3937618400316066</v>
       </c>
       <c r="S9">
-        <v>0.3937618400316066</v>
+        <v>0.01684119700686856</v>
       </c>
       <c r="T9">
-        <v>0.01684119700686856</v>
+        <v>0.4780748453849443</v>
+      </c>
+      <c r="U9">
+        <v>0.01384921261474243</v>
+      </c>
+      <c r="V9">
+        <v>0.2609203730861911</v>
+      </c>
+      <c r="W9">
+        <v>0.008272674065063514</v>
+      </c>
+      <c r="X9">
+        <v>0.4129389365958673</v>
+      </c>
+      <c r="Y9">
+        <v>0.008150115983215958</v>
+      </c>
+      <c r="Z9">
+        <v>9.614197501883453</v>
+      </c>
+      <c r="AA9">
+        <v>0.7956497162307288</v>
+      </c>
+      <c r="AB9">
+        <v>0.05565468343785564</v>
+      </c>
+      <c r="AC9">
+        <v>0.01003222662159669</v>
       </c>
     </row>
     <row r="10">
@@ -975,61 +1236,88 @@
         </is>
       </c>
       <c r="B10">
-        <v>50</v>
+        <v>0.6414901403176531</v>
       </c>
       <c r="C10">
-        <v>0.6414901403176531</v>
+        <v>0.004273619870648413</v>
       </c>
       <c r="D10">
-        <v>0.004273619870648413</v>
+        <v>0.6099903785480748</v>
       </c>
       <c r="E10">
+        <v>0.002920748011074626</v>
+      </c>
+      <c r="F10">
+        <v>0.7798253177106312</v>
+      </c>
+      <c r="G10">
+        <v>0.002212694509758641</v>
+      </c>
+      <c r="H10">
+        <v>5.147584163317431</v>
+      </c>
+      <c r="I10">
+        <v>0.08453764155103688</v>
+      </c>
+      <c r="J10">
         <v>0.3187694963196284</v>
       </c>
-      <c r="F10">
+      <c r="K10">
         <v>0.002373654033742705</v>
       </c>
-      <c r="G10">
-        <v>0.6099903785480748</v>
-      </c>
-      <c r="H10">
-        <v>0.002920748011074626</v>
-      </c>
-      <c r="I10">
+      <c r="L10">
         <v>0.2648722199561907</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>0.002489031892597551</v>
       </c>
-      <c r="K10">
-        <v>0.7798253177106312</v>
-      </c>
-      <c r="L10">
-        <v>0.002212694509758641</v>
-      </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.3386275455218445</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.003825206015149443</v>
       </c>
-      <c r="O10">
-        <v>5.147584163317431</v>
-      </c>
       <c r="P10">
-        <v>0.08453764155103688</v>
+        <v>2.235801900355239</v>
       </c>
       <c r="Q10">
-        <v>2.235801900355239</v>
+        <v>0.06639150848013753</v>
       </c>
       <c r="R10">
-        <v>0.06639150848013753</v>
+        <v>0.496965930382727</v>
       </c>
       <c r="S10">
-        <v>0.496965930382727</v>
+        <v>0.006999646773827817</v>
       </c>
       <c r="T10">
-        <v>0.006999646773827817</v>
+        <v>0.1023557249535129</v>
+      </c>
+      <c r="U10">
+        <v>0.009401266084555788</v>
+      </c>
+      <c r="V10">
+        <v>0.01087137128068802</v>
+      </c>
+      <c r="W10">
+        <v>0.002729901209844177</v>
+      </c>
+      <c r="X10">
+        <v>0.02871951737993734</v>
+      </c>
+      <c r="Y10">
+        <v>0.003846864812893103</v>
+      </c>
+      <c r="Z10">
+        <v>59.05599396809212</v>
+      </c>
+      <c r="AA10">
+        <v>4.42721178736164</v>
+      </c>
+      <c r="AB10">
+        <v>0.02713106093417507</v>
+      </c>
+      <c r="AC10">
+        <v>0.003176159807762584</v>
       </c>
     </row>
     <row r="11">
@@ -1039,61 +1327,88 @@
         </is>
       </c>
       <c r="B11">
-        <v>50</v>
+        <v>0.8901877684107996</v>
       </c>
       <c r="C11">
-        <v>0.8901877684107996</v>
+        <v>0.004225369425558708</v>
       </c>
       <c r="D11">
-        <v>0.004225369425558708</v>
+        <v>0.8485281004061611</v>
       </c>
       <c r="E11">
+        <v>0.00527278305019368</v>
+      </c>
+      <c r="F11">
+        <v>0.930193489689581</v>
+      </c>
+      <c r="G11">
+        <v>0.002739022400968173</v>
+      </c>
+      <c r="H11">
+        <v>2.149537981498588</v>
+      </c>
+      <c r="I11">
+        <v>0.08182449002028211</v>
+      </c>
+      <c r="J11">
         <v>0.1264056104877833</v>
       </c>
-      <c r="F11">
+      <c r="K11">
         <v>0.004345377490116616</v>
       </c>
-      <c r="G11">
-        <v>0.8485281004061611</v>
-      </c>
-      <c r="H11">
-        <v>0.00527278305019368</v>
-      </c>
-      <c r="I11">
+      <c r="L11">
         <v>0.1052793904060438</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>0.003475722012218523</v>
       </c>
-      <c r="K11">
-        <v>0.930193489689581</v>
-      </c>
-      <c r="L11">
-        <v>0.002739022400968173</v>
-      </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.1154260407350178</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.004182761391456683</v>
       </c>
-      <c r="O11">
-        <v>2.149537981498588</v>
-      </c>
       <c r="P11">
-        <v>0.08182449002028211</v>
+        <v>0.2671425402749656</v>
       </c>
       <c r="Q11">
-        <v>0.2671425402749656</v>
+        <v>0.02060114557610118</v>
       </c>
       <c r="R11">
-        <v>0.02060114557610118</v>
+        <v>0.1420245601712867</v>
       </c>
       <c r="S11">
-        <v>0.1420245601712867</v>
+        <v>0.005560884276298028</v>
       </c>
       <c r="T11">
-        <v>0.005560884276298028</v>
+        <v>0.1397701949056407</v>
+      </c>
+      <c r="U11">
+        <v>0.01226429600279236</v>
+      </c>
+      <c r="V11">
+        <v>0.03706035136206266</v>
+      </c>
+      <c r="W11">
+        <v>0.003629757905330099</v>
+      </c>
+      <c r="X11">
+        <v>0.05934026749197196</v>
+      </c>
+      <c r="Y11">
+        <v>0.007555167833599085</v>
+      </c>
+      <c r="Z11">
+        <v>51.75412540277419</v>
+      </c>
+      <c r="AA11">
+        <v>2.475561370024738</v>
+      </c>
+      <c r="AB11">
+        <v>0.1490972706581207</v>
+      </c>
+      <c r="AC11">
+        <v>0.01320838609252158</v>
       </c>
     </row>
     <row r="12">
@@ -1103,61 +1418,88 @@
         </is>
       </c>
       <c r="B12">
-        <v>50</v>
+        <v>0.7111708495462642</v>
       </c>
       <c r="C12">
-        <v>0.7111708495462642</v>
+        <v>0.006466917756339929</v>
       </c>
       <c r="D12">
-        <v>0.006466917756339929</v>
+        <v>0.6626436606730192</v>
       </c>
       <c r="E12">
+        <v>0.005473775449700998</v>
+      </c>
+      <c r="F12">
+        <v>0.8180711873800699</v>
+      </c>
+      <c r="G12">
+        <v>0.003818144318990473</v>
+      </c>
+      <c r="H12">
+        <v>4.063535059222295</v>
+      </c>
+      <c r="I12">
+        <v>0.1046545745111825</v>
+      </c>
+      <c r="J12">
         <v>0.2759828013114681</v>
       </c>
-      <c r="F12">
+      <c r="K12">
         <v>0.004266292287682055</v>
       </c>
-      <c r="G12">
-        <v>0.6626436606730192</v>
-      </c>
-      <c r="H12">
-        <v>0.005473775449700998</v>
-      </c>
-      <c r="I12">
+      <c r="L12">
         <v>0.2247051867215604</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>0.003699157146149366</v>
       </c>
-      <c r="K12">
-        <v>0.8180711873800699</v>
-      </c>
-      <c r="L12">
-        <v>0.003818144318990473</v>
-      </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.2774348588006091</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.005537267549478905</v>
       </c>
-      <c r="O12">
-        <v>4.063535059222295</v>
-      </c>
       <c r="P12">
-        <v>0.1046545745111825</v>
+        <v>1.379059688204052</v>
       </c>
       <c r="Q12">
-        <v>1.379059688204052</v>
+        <v>0.06906509006607682</v>
       </c>
       <c r="R12">
-        <v>0.06906509006607682</v>
+        <v>0.3881528121162313</v>
       </c>
       <c r="S12">
-        <v>0.3881528121162313</v>
+        <v>0.009531105955838557</v>
       </c>
       <c r="T12">
-        <v>0.009531105955838557</v>
+        <v>0.1550598213977584</v>
+      </c>
+      <c r="U12">
+        <v>0.008442653353714543</v>
+      </c>
+      <c r="V12">
+        <v>0.03058281292213921</v>
+      </c>
+      <c r="W12">
+        <v>0.003540676993024374</v>
+      </c>
+      <c r="X12">
+        <v>0.04831554644994982</v>
+      </c>
+      <c r="Y12">
+        <v>0.004356480793293855</v>
+      </c>
+      <c r="Z12">
+        <v>56.05313579146441</v>
+      </c>
+      <c r="AA12">
+        <v>3.431749212952457</v>
+      </c>
+      <c r="AB12">
+        <v>0.06456473210619906</v>
+      </c>
+      <c r="AC12">
+        <v>0.004800194512121427</v>
       </c>
     </row>
     <row r="13">
@@ -1167,61 +1509,88 @@
         </is>
       </c>
       <c r="B13">
-        <v>50</v>
+        <v>0.9631000704022525</v>
       </c>
       <c r="C13">
-        <v>0.9631000704022525</v>
+        <v>0.002564163105226071</v>
       </c>
       <c r="D13">
-        <v>0.002564163105226071</v>
+        <v>0.9470760557488132</v>
       </c>
       <c r="E13">
+        <v>0.003562976226902971</v>
+      </c>
+      <c r="F13">
+        <v>0.9774935672790238</v>
+      </c>
+      <c r="G13">
+        <v>0.001581414779757471</v>
+      </c>
+      <c r="H13">
+        <v>0.3804630662594367</v>
+      </c>
+      <c r="I13">
+        <v>0.03429580739577314</v>
+      </c>
+      <c r="J13">
         <v>0.04715354148183693</v>
       </c>
-      <c r="F13">
+      <c r="K13">
         <v>0.003158805830109133</v>
       </c>
-      <c r="G13">
-        <v>0.9470760557488132</v>
-      </c>
-      <c r="H13">
-        <v>0.003562976226902971</v>
-      </c>
-      <c r="I13">
+      <c r="L13">
         <v>0.04051452225500111</v>
       </c>
-      <c r="J13">
+      <c r="M13">
         <v>0.002669161744256987</v>
       </c>
-      <c r="K13">
-        <v>0.9774935672790238</v>
-      </c>
-      <c r="L13">
-        <v>0.001581414779757471</v>
-      </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.04182183270007519</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.002846558597234428</v>
       </c>
-      <c r="O13">
-        <v>0.3804630662594367</v>
-      </c>
       <c r="P13">
-        <v>0.03429580739577314</v>
+        <v>0.01637499764835196</v>
       </c>
       <c r="Q13">
-        <v>0.01637499764835196</v>
+        <v>0.002610903270249857</v>
       </c>
       <c r="R13">
-        <v>0.002610903270249857</v>
+        <v>0.04896906322399475</v>
       </c>
       <c r="S13">
-        <v>0.04896906322399475</v>
+        <v>0.003413710605562046</v>
       </c>
       <c r="T13">
-        <v>0.003413710605562046</v>
+        <v>0.03803966353197402</v>
+      </c>
+      <c r="U13">
+        <v>0.005142854572533952</v>
+      </c>
+      <c r="V13">
+        <v>0.009124320361391294</v>
+      </c>
+      <c r="W13">
+        <v>0.001625304284932404</v>
+      </c>
+      <c r="X13">
+        <v>0.01375709499175029</v>
+      </c>
+      <c r="Y13">
+        <v>0.003843806886159128</v>
+      </c>
+      <c r="Z13">
+        <v>7.141045142518886</v>
+      </c>
+      <c r="AA13">
+        <v>0.7093497631197466</v>
+      </c>
+      <c r="AB13">
+        <v>0.05902475223378458</v>
+      </c>
+      <c r="AC13">
+        <v>0.007921442429667021</v>
       </c>
     </row>
     <row r="14">
@@ -1231,61 +1600,88 @@
         </is>
       </c>
       <c r="B14">
-        <v>50</v>
+        <v>0.742029021850248</v>
       </c>
       <c r="C14">
-        <v>0.742029021850248</v>
+        <v>0.01905299109839132</v>
       </c>
       <c r="D14">
-        <v>0.01905299109839132</v>
+        <v>0.6418683024171311</v>
       </c>
       <c r="E14">
+        <v>0.02398385813532614</v>
+      </c>
+      <c r="F14">
+        <v>0.803049470159281</v>
+      </c>
+      <c r="G14">
+        <v>0.01740425564286841</v>
+      </c>
+      <c r="H14">
+        <v>1.057151337133986</v>
+      </c>
+      <c r="I14">
+        <v>0.0685275085310853</v>
+      </c>
+      <c r="J14">
         <v>0.213377108516645</v>
       </c>
-      <c r="F14">
+      <c r="K14">
         <v>0.007791818087010946</v>
       </c>
-      <c r="G14">
-        <v>0.6418683024171311</v>
-      </c>
-      <c r="H14">
-        <v>0.02398385813532614</v>
-      </c>
-      <c r="I14">
+      <c r="L14">
         <v>0.1611683114471189</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>0.004044165078079826</v>
       </c>
-      <c r="K14">
-        <v>0.803049470159281</v>
-      </c>
-      <c r="L14">
-        <v>0.01740425564286841</v>
-      </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.2018332831123106</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.008206000292314346</v>
       </c>
-      <c r="O14">
-        <v>1.057151337133986</v>
-      </c>
       <c r="P14">
-        <v>0.0685275085310853</v>
+        <v>0.2670742437511748</v>
       </c>
       <c r="Q14">
-        <v>0.2670742437511748</v>
+        <v>0.03416920458692329</v>
       </c>
       <c r="R14">
-        <v>0.03416920458692329</v>
+        <v>0.2880115166596838</v>
       </c>
       <c r="S14">
-        <v>0.2880115166596838</v>
+        <v>0.01801884108557721</v>
       </c>
       <c r="T14">
-        <v>0.01801884108557721</v>
+        <v>0.3981922180694976</v>
+      </c>
+      <c r="U14">
+        <v>0.02639339076327003</v>
+      </c>
+      <c r="V14">
+        <v>0.1914111574996817</v>
+      </c>
+      <c r="W14">
+        <v>0.01774235347754017</v>
+      </c>
+      <c r="X14">
+        <v>0.2999907561667416</v>
+      </c>
+      <c r="Y14">
+        <v>0.02719779166839709</v>
+      </c>
+      <c r="Z14">
+        <v>8.253197389959757</v>
+      </c>
+      <c r="AA14">
+        <v>0.7679348547145697</v>
+      </c>
+      <c r="AB14">
+        <v>0.1226057590530637</v>
+      </c>
+      <c r="AC14">
+        <v>0.01244355018085732</v>
       </c>
     </row>
     <row r="15">
@@ -1295,61 +1691,88 @@
         </is>
       </c>
       <c r="B15">
-        <v>50</v>
+        <v>0.9349450337047209</v>
       </c>
       <c r="C15">
-        <v>0.9349450337047209</v>
+        <v>0.009695873906593594</v>
       </c>
       <c r="D15">
-        <v>0.009695873906593594</v>
+        <v>0.9049911083035646</v>
       </c>
       <c r="E15">
+        <v>0.01366190384946476</v>
+      </c>
+      <c r="F15">
+        <v>0.9581343799255708</v>
+      </c>
+      <c r="G15">
+        <v>0.006508956568449406</v>
+      </c>
+      <c r="H15">
+        <v>0.3944665032145837</v>
+      </c>
+      <c r="I15">
+        <v>0.04253158757802413</v>
+      </c>
+      <c r="J15">
         <v>0.07683001910598108</v>
       </c>
-      <c r="F15">
+      <c r="K15">
         <v>0.01032462025167843</v>
       </c>
-      <c r="G15">
-        <v>0.9049911083035646</v>
-      </c>
-      <c r="H15">
-        <v>0.01366190384946476</v>
-      </c>
-      <c r="I15">
+      <c r="L15">
         <v>0.06494009042439357</v>
       </c>
-      <c r="J15">
+      <c r="M15">
         <v>0.008408726541694094</v>
       </c>
-      <c r="K15">
-        <v>0.9581343799255708</v>
-      </c>
-      <c r="L15">
-        <v>0.006508956568449406</v>
-      </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.06883482126093812</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.009507257268193054</v>
       </c>
-      <c r="O15">
-        <v>0.3944665032145837</v>
-      </c>
       <c r="P15">
-        <v>0.04253158757802413</v>
+        <v>0.02877561565516347</v>
       </c>
       <c r="Q15">
-        <v>0.02877561565516347</v>
+        <v>0.007297161351508334</v>
       </c>
       <c r="R15">
-        <v>0.007297161351508334</v>
+        <v>0.08229738157998262</v>
       </c>
       <c r="S15">
-        <v>0.08229738157998262</v>
+        <v>0.01195091149181808</v>
       </c>
       <c r="T15">
-        <v>0.01195091149181808</v>
+        <v>0.08351499619338398</v>
+      </c>
+      <c r="U15">
+        <v>0.01861419662774795</v>
+      </c>
+      <c r="V15">
+        <v>0.02490387503589981</v>
+      </c>
+      <c r="W15">
+        <v>0.005152193917769431</v>
+      </c>
+      <c r="X15">
+        <v>0.0368184682025211</v>
+      </c>
+      <c r="Y15">
+        <v>0.01092897443296651</v>
+      </c>
+      <c r="Z15">
+        <v>3.770089277785117</v>
+      </c>
+      <c r="AA15">
+        <v>0.3465121530472487</v>
+      </c>
+      <c r="AB15">
+        <v>0.100589217120909</v>
+      </c>
+      <c r="AC15">
+        <v>0.01745205486442951</v>
       </c>
     </row>
     <row r="16">
@@ -1359,61 +1782,88 @@
         </is>
       </c>
       <c r="B16">
-        <v>50</v>
+        <v>0.99335750581699</v>
       </c>
       <c r="C16">
-        <v>0.99335750581699</v>
+        <v>0.001110280571653551</v>
       </c>
       <c r="D16">
-        <v>0.001110280571653551</v>
+        <v>0.9899730551582056</v>
       </c>
       <c r="E16">
+        <v>0.001659887660708658</v>
+      </c>
+      <c r="F16">
+        <v>0.9958799068888505</v>
+      </c>
+      <c r="G16">
+        <v>0.0006877077671356849</v>
+      </c>
+      <c r="H16">
+        <v>0.1157919446998024</v>
+      </c>
+      <c r="I16">
+        <v>0.01713202523886006</v>
+      </c>
+      <c r="J16">
         <v>0.00853944846607909</v>
       </c>
-      <c r="F16">
+      <c r="K16">
         <v>0.001421712329311906</v>
       </c>
-      <c r="G16">
-        <v>0.9899730551582056</v>
-      </c>
-      <c r="H16">
-        <v>0.001659887660708658</v>
-      </c>
-      <c r="I16">
+      <c r="L16">
         <v>0.007435717283518019</v>
       </c>
-      <c r="J16">
+      <c r="M16">
         <v>0.001233635600051623</v>
       </c>
-      <c r="K16">
-        <v>0.9958799068888505</v>
-      </c>
-      <c r="L16">
-        <v>0.0006877077671356849</v>
-      </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.007481295515426618</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.001248891652291973</v>
       </c>
-      <c r="O16">
-        <v>0.1157919446998024</v>
-      </c>
       <c r="P16">
-        <v>0.01713202523886006</v>
+        <v>0.0008886441211891369</v>
       </c>
       <c r="Q16">
-        <v>0.0008886441211891369</v>
+        <v>0.0002734260886384048</v>
       </c>
       <c r="R16">
-        <v>0.0002734260886384048</v>
+        <v>0.008598129792789627</v>
       </c>
       <c r="S16">
-        <v>0.008598129792789627</v>
+        <v>0.001441527833442053</v>
       </c>
       <c r="T16">
-        <v>0.001441527833442053</v>
+        <v>0.006923143680618762</v>
+      </c>
+      <c r="U16">
+        <v>0.002635813056071557</v>
+      </c>
+      <c r="V16">
+        <v>0.001843012517090527</v>
+      </c>
+      <c r="W16">
+        <v>0.0005693519331749675</v>
+      </c>
+      <c r="X16">
+        <v>0.002586915664556421</v>
+      </c>
+      <c r="Y16">
+        <v>0.001801188567841182</v>
+      </c>
+      <c r="Z16">
+        <v>2.260488816466844</v>
+      </c>
+      <c r="AA16">
+        <v>0.3871230959850769</v>
+      </c>
+      <c r="AB16">
+        <v>0.01118616826028611</v>
+      </c>
+      <c r="AC16">
+        <v>0.004238761569422502</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Convex_combination/Clustering/n10000/Summary_Statistics.xlsx
+++ b/Results/Convex_combination/Clustering/n10000/Summary_Statistics.xlsx
@@ -963,88 +963,88 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.4433662313490916</v>
+        <v>0.5151525226987883</v>
       </c>
       <c r="C7">
-        <v>0.005796336087793892</v>
+        <v>0.01185341091922567</v>
       </c>
       <c r="D7">
-        <v>0.3658834401553669</v>
+        <v>0.413106631911038</v>
       </c>
       <c r="E7">
-        <v>0.003181042924385274</v>
+        <v>0.008777597646106607</v>
       </c>
       <c r="F7">
-        <v>0.5539521972147431</v>
+        <v>0.6046856362904065</v>
       </c>
       <c r="G7">
-        <v>0.003551530833275082</v>
+        <v>0.009086712984963044</v>
       </c>
       <c r="H7">
-        <v>2.813577176459131</v>
+        <v>2.144800757908613</v>
       </c>
       <c r="I7">
-        <v>0.06642518107114648</v>
+        <v>0.09417060759548199</v>
       </c>
       <c r="J7">
-        <v>0.2783170922741619</v>
+        <v>0.2716142016106999</v>
       </c>
       <c r="K7">
-        <v>0.0004663156017755403</v>
+        <v>0.001660919049179214</v>
       </c>
       <c r="L7">
-        <v>0.200707112856849</v>
+        <v>0.1903341679999175</v>
       </c>
       <c r="M7">
-        <v>0.001224193595661112</v>
+        <v>0.001550550115514257</v>
       </c>
       <c r="N7">
-        <v>0.3038828899372524</v>
+        <v>0.2786508994336188</v>
       </c>
       <c r="O7">
-        <v>0.002511337934419945</v>
+        <v>0.003930538136860543</v>
       </c>
       <c r="P7">
-        <v>1.544073721646477</v>
+        <v>0.9899839104514545</v>
       </c>
       <c r="Q7">
-        <v>0.05809490763716704</v>
+        <v>0.07171567331836701</v>
       </c>
       <c r="R7">
-        <v>0.6278531135417441</v>
+        <v>0.5275940313049715</v>
       </c>
       <c r="S7">
-        <v>0.009133473020499903</v>
+        <v>0.01527754938703064</v>
       </c>
       <c r="T7">
-        <v>0.2076610790953174</v>
+        <v>0.3846349471979695</v>
       </c>
       <c r="U7">
-        <v>0.01647300664666101</v>
+        <v>0.02434355345892947</v>
       </c>
       <c r="V7">
-        <v>0.1049516086284012</v>
+        <v>0.1891053656005399</v>
       </c>
       <c r="W7">
-        <v>0.01074594235585463</v>
+        <v>0.01514659079209568</v>
       </c>
       <c r="X7">
-        <v>0.165683462113652</v>
+        <v>0.3002523629006691</v>
       </c>
       <c r="Y7">
-        <v>0.01117925294545052</v>
+        <v>0.02022855521123102</v>
       </c>
       <c r="Z7">
-        <v>17.32858731044854</v>
+        <v>15.14965353373947</v>
       </c>
       <c r="AA7">
-        <v>1.445334382446014</v>
+        <v>0.9315230647283174</v>
       </c>
       <c r="AB7">
-        <v>0.009372440322686398</v>
+        <v>0.007904853661870175</v>
       </c>
       <c r="AC7">
-        <v>0.0007038860435488718</v>
+        <v>0.001643933327095412</v>
       </c>
     </row>
     <row r="8">
@@ -1054,88 +1054,88 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.5332070492323669</v>
+        <v>0.6732205139479757</v>
       </c>
       <c r="C8">
-        <v>0.01308951821763429</v>
+        <v>0.0180074670419026</v>
       </c>
       <c r="D8">
-        <v>0.4269797168269326</v>
+        <v>0.5667876906825611</v>
       </c>
       <c r="E8">
-        <v>0.01026478687519261</v>
+        <v>0.02168633189628468</v>
       </c>
       <c r="F8">
-        <v>0.6188746111170528</v>
+        <v>0.7456611747327661</v>
       </c>
       <c r="G8">
-        <v>0.01040084684666018</v>
+        <v>0.01767340456107068</v>
       </c>
       <c r="H8">
-        <v>2.017768717373423</v>
+        <v>1.606441176910535</v>
       </c>
       <c r="I8">
-        <v>0.08827033418810416</v>
+        <v>0.0210302517407413</v>
       </c>
       <c r="J8">
-        <v>0.2690965015844677</v>
+        <v>0.2444301750717919</v>
       </c>
       <c r="K8">
-        <v>0.00201430682859187</v>
+        <v>0.003823236651044451</v>
       </c>
       <c r="L8">
-        <v>0.1882966589325888</v>
+        <v>0.1797323492244948</v>
       </c>
       <c r="M8">
-        <v>0.001561055969453872</v>
+        <v>0.000943387077181422</v>
       </c>
       <c r="N8">
-        <v>0.272983257516994</v>
+        <v>0.2365975875220663</v>
       </c>
       <c r="O8">
-        <v>0.004172316562023845</v>
+        <v>0.004451530408409953</v>
       </c>
       <c r="P8">
-        <v>0.8916901258429473</v>
+        <v>0.5102308509776134</v>
       </c>
       <c r="Q8">
-        <v>0.06732174177100243</v>
+        <v>0.0230018018409545</v>
       </c>
       <c r="R8">
-        <v>0.505063536388268</v>
+        <v>0.3634814067337032</v>
       </c>
       <c r="S8">
-        <v>0.01615407298275467</v>
+        <v>0.01549746929616794</v>
       </c>
       <c r="T8">
-        <v>0.4193906893807232</v>
+        <v>0.4365950980187056</v>
       </c>
       <c r="U8">
-        <v>0.02305672569360686</v>
+        <v>0.02781974037993577</v>
       </c>
       <c r="V8">
-        <v>0.2076208746055073</v>
+        <v>0.2451769745568355</v>
       </c>
       <c r="W8">
-        <v>0.01547269747708014</v>
+        <v>0.01460492956422258</v>
       </c>
       <c r="X8">
-        <v>0.3300048132597305</v>
+        <v>0.3863431717164688</v>
       </c>
       <c r="Y8">
-        <v>0.02061248439586613</v>
+        <v>0.02191069998353674</v>
       </c>
       <c r="Z8">
-        <v>14.34117085782104</v>
+        <v>9.390087771045847</v>
       </c>
       <c r="AA8">
-        <v>0.9508355975949571</v>
+        <v>0.7485077404328102</v>
       </c>
       <c r="AB8">
-        <v>0.01113452608971342</v>
+        <v>0.07408076265804241</v>
       </c>
       <c r="AC8">
-        <v>0.002871533019853966</v>
+        <v>0.009613239142752559</v>
       </c>
     </row>
     <row r="9">
@@ -1145,88 +1145,88 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.6386694171505568</v>
+        <v>0.7763757027813102</v>
       </c>
       <c r="C9">
-        <v>0.01811872317724497</v>
+        <v>0.01240569241640752</v>
       </c>
       <c r="D9">
-        <v>0.5266091847064053</v>
+        <v>0.7077983058852025</v>
       </c>
       <c r="E9">
-        <v>0.01977537421308335</v>
+        <v>0.01837647284834793</v>
       </c>
       <c r="F9">
-        <v>0.7120382460216492</v>
+        <v>0.8482697513587071</v>
       </c>
       <c r="G9">
-        <v>0.01716867976140488</v>
+        <v>0.01197802215213614</v>
       </c>
       <c r="H9">
-        <v>1.630461826468364</v>
+        <v>1.827386143027371</v>
       </c>
       <c r="I9">
-        <v>0.0328005125735916</v>
+        <v>0.07015224496650939</v>
       </c>
       <c r="J9">
-        <v>0.2511850948374495</v>
+        <v>0.2171703245519144</v>
       </c>
       <c r="K9">
-        <v>0.003549703365950419</v>
+        <v>0.004565914233634498</v>
       </c>
       <c r="L9">
-        <v>0.1809073274074718</v>
+        <v>0.1729422738267005</v>
       </c>
       <c r="M9">
-        <v>0.001046333038321472</v>
+        <v>0.0021110516399021</v>
       </c>
       <c r="N9">
-        <v>0.2447454307216</v>
+        <v>0.2073522508509487</v>
       </c>
       <c r="O9">
-        <v>0.004533428535744368</v>
+        <v>0.004784448249892042</v>
       </c>
       <c r="P9">
-        <v>0.5613708034519127</v>
+        <v>0.4464106912083023</v>
       </c>
       <c r="Q9">
-        <v>0.03397062663556095</v>
+        <v>0.01028626623146859</v>
       </c>
       <c r="R9">
-        <v>0.3937618400316066</v>
+        <v>0.2798838762342001</v>
       </c>
       <c r="S9">
-        <v>0.01684119700686856</v>
+        <v>0.0103403368037106</v>
       </c>
       <c r="T9">
-        <v>0.4780748453849443</v>
+        <v>0.1905785026916887</v>
       </c>
       <c r="U9">
-        <v>0.01384921261474243</v>
+        <v>0.03447123707429943</v>
       </c>
       <c r="V9">
-        <v>0.2609203730861911</v>
+        <v>0.09472882572965663</v>
       </c>
       <c r="W9">
-        <v>0.008272674065063514</v>
+        <v>0.02387627904664912</v>
       </c>
       <c r="X9">
-        <v>0.4129389365958673</v>
+        <v>0.1498762714652795</v>
       </c>
       <c r="Y9">
-        <v>0.008150115983215958</v>
+        <v>0.03651525122365496</v>
       </c>
       <c r="Z9">
-        <v>9.614197501883453</v>
+        <v>18.04778700836314</v>
       </c>
       <c r="AA9">
-        <v>0.7956497162307288</v>
+        <v>2.571848492555791</v>
       </c>
       <c r="AB9">
-        <v>0.05565468343785564</v>
+        <v>0.0933670293782697</v>
       </c>
       <c r="AC9">
-        <v>0.01003222662159669</v>
+        <v>0.006195017520366463</v>
       </c>
     </row>
     <row r="10">
@@ -1327,88 +1327,88 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.8901877684107996</v>
+        <v>0.8749321575864998</v>
       </c>
       <c r="C11">
-        <v>0.004225369425558708</v>
+        <v>0.005582705388291708</v>
       </c>
       <c r="D11">
-        <v>0.8485281004061611</v>
+        <v>0.8335751921175348</v>
       </c>
       <c r="E11">
-        <v>0.00527278305019368</v>
+        <v>0.006312505385213342</v>
       </c>
       <c r="F11">
-        <v>0.930193489689581</v>
+        <v>0.9223430079803376</v>
       </c>
       <c r="G11">
-        <v>0.002739022400968173</v>
+        <v>0.003347474279025483</v>
       </c>
       <c r="H11">
-        <v>2.149537981498588</v>
+        <v>2.260917703194973</v>
       </c>
       <c r="I11">
-        <v>0.08182449002028211</v>
+        <v>0.09543149471498941</v>
       </c>
       <c r="J11">
-        <v>0.1264056104877833</v>
+        <v>0.1438181179223706</v>
       </c>
       <c r="K11">
-        <v>0.004345377490116616</v>
+        <v>0.005852065641904795</v>
       </c>
       <c r="L11">
-        <v>0.1052793904060438</v>
+        <v>0.1197224026513358</v>
       </c>
       <c r="M11">
-        <v>0.003475722012218523</v>
+        <v>0.004732077826236864</v>
       </c>
       <c r="N11">
-        <v>0.1154260407350178</v>
+        <v>0.1324957289897988</v>
       </c>
       <c r="O11">
-        <v>0.004182761391456683</v>
+        <v>0.005752082886234918</v>
       </c>
       <c r="P11">
-        <v>0.2671425402749656</v>
+        <v>0.3254313954759816</v>
       </c>
       <c r="Q11">
-        <v>0.02060114557610118</v>
+        <v>0.02842247172711878</v>
       </c>
       <c r="R11">
-        <v>0.1420245601712867</v>
+        <v>0.1644246086440879</v>
       </c>
       <c r="S11">
-        <v>0.005560884276298028</v>
+        <v>0.007726873992023038</v>
       </c>
       <c r="T11">
-        <v>0.1397701949056407</v>
+        <v>0.1778041828735975</v>
       </c>
       <c r="U11">
-        <v>0.01226429600279236</v>
+        <v>0.009828745135816103</v>
       </c>
       <c r="V11">
-        <v>0.03706035136206266</v>
+        <v>0.04066119339014405</v>
       </c>
       <c r="W11">
-        <v>0.003629757905330099</v>
+        <v>0.002380711295600335</v>
       </c>
       <c r="X11">
-        <v>0.05934026749197196</v>
+        <v>0.06392408229671366</v>
       </c>
       <c r="Y11">
-        <v>0.007555167833599085</v>
+        <v>0.005742547085555575</v>
       </c>
       <c r="Z11">
-        <v>51.75412540277419</v>
+        <v>59.80648199857379</v>
       </c>
       <c r="AA11">
-        <v>2.475561370024738</v>
+        <v>2.860610542160025</v>
       </c>
       <c r="AB11">
-        <v>0.1490972706581207</v>
+        <v>0.1945974984051364</v>
       </c>
       <c r="AC11">
-        <v>0.01320838609252158</v>
+        <v>0.009726707995719334</v>
       </c>
     </row>
     <row r="12">
@@ -1600,88 +1600,88 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.742029021850248</v>
+        <v>0.9137233231167142</v>
       </c>
       <c r="C14">
-        <v>0.01905299109839132</v>
+        <v>0.01123718192927351</v>
       </c>
       <c r="D14">
-        <v>0.6418683024171311</v>
+        <v>0.8749902871942461</v>
       </c>
       <c r="E14">
-        <v>0.02398385813532614</v>
+        <v>0.01575963989048742</v>
       </c>
       <c r="F14">
-        <v>0.803049470159281</v>
+        <v>0.9435432177617118</v>
       </c>
       <c r="G14">
-        <v>0.01740425564286841</v>
+        <v>0.007886408169713267</v>
       </c>
       <c r="H14">
-        <v>1.057151337133986</v>
+        <v>0.4785425017924044</v>
       </c>
       <c r="I14">
-        <v>0.0685275085310853</v>
+        <v>0.04496966986284615</v>
       </c>
       <c r="J14">
-        <v>0.213377108516645</v>
+        <v>0.09847862021907149</v>
       </c>
       <c r="K14">
-        <v>0.007791818087010946</v>
+        <v>0.01097373055566331</v>
       </c>
       <c r="L14">
-        <v>0.1611683114471189</v>
+        <v>0.08234646531034044</v>
       </c>
       <c r="M14">
-        <v>0.004044165078079826</v>
+        <v>0.008690768246802547</v>
       </c>
       <c r="N14">
-        <v>0.2018332831123106</v>
+        <v>0.08890241434575165</v>
       </c>
       <c r="O14">
-        <v>0.008206000292314346</v>
+        <v>0.01027086223875231</v>
       </c>
       <c r="P14">
-        <v>0.2670742437511748</v>
+        <v>0.04562249493605415</v>
       </c>
       <c r="Q14">
-        <v>0.03416920458692329</v>
+        <v>0.009957692874770392</v>
       </c>
       <c r="R14">
-        <v>0.2880115166596838</v>
+        <v>0.1079387739909487</v>
       </c>
       <c r="S14">
-        <v>0.01801884108557721</v>
+        <v>0.01340910647625251</v>
       </c>
       <c r="T14">
-        <v>0.3981922180694976</v>
+        <v>0.1175931986482248</v>
       </c>
       <c r="U14">
-        <v>0.02639339076327003</v>
+        <v>0.02080109218419797</v>
       </c>
       <c r="V14">
-        <v>0.1914111574996817</v>
+        <v>0.03709423811435036</v>
       </c>
       <c r="W14">
-        <v>0.01774235347754017</v>
+        <v>0.007656778268965775</v>
       </c>
       <c r="X14">
-        <v>0.2999907561667416</v>
+        <v>0.05607159818775435</v>
       </c>
       <c r="Y14">
-        <v>0.02719779166839709</v>
+        <v>0.01335293682986013</v>
       </c>
       <c r="Z14">
-        <v>8.253197389959757</v>
+        <v>4.249892116406888</v>
       </c>
       <c r="AA14">
-        <v>0.7679348547145697</v>
+        <v>0.3344037868685192</v>
       </c>
       <c r="AB14">
-        <v>0.1226057590530637</v>
+        <v>0.125746752836536</v>
       </c>
       <c r="AC14">
-        <v>0.01244355018085732</v>
+        <v>0.01449737096349169</v>
       </c>
     </row>
     <row r="15">
@@ -1691,88 +1691,88 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9349450337047209</v>
+        <v>0.993072580701494</v>
       </c>
       <c r="C15">
-        <v>0.009695873906593594</v>
+        <v>0.001280436081574029</v>
       </c>
       <c r="D15">
-        <v>0.9049911083035646</v>
+        <v>0.9895539357266224</v>
       </c>
       <c r="E15">
-        <v>0.01366190384946476</v>
+        <v>0.001928294593280812</v>
       </c>
       <c r="F15">
-        <v>0.9581343799255708</v>
+        <v>0.9957059818337408</v>
       </c>
       <c r="G15">
-        <v>0.006508956568449406</v>
+        <v>0.000800014161913692</v>
       </c>
       <c r="H15">
-        <v>0.3944665032145837</v>
+        <v>0.1215958441116</v>
       </c>
       <c r="I15">
-        <v>0.04253158757802413</v>
+        <v>0.0173559219204826</v>
       </c>
       <c r="J15">
-        <v>0.07683001910598108</v>
+        <v>0.008917920938243619</v>
       </c>
       <c r="K15">
-        <v>0.01032462025167843</v>
+        <v>0.001627671831214322</v>
       </c>
       <c r="L15">
-        <v>0.06494009042439357</v>
+        <v>0.007764001594155658</v>
       </c>
       <c r="M15">
-        <v>0.008408726541694094</v>
+        <v>0.001411367628427215</v>
       </c>
       <c r="N15">
-        <v>0.06883482126093812</v>
+        <v>0.007813883031340818</v>
       </c>
       <c r="O15">
-        <v>0.009507257268193054</v>
+        <v>0.001430391403872025</v>
       </c>
       <c r="P15">
-        <v>0.02877561565516347</v>
+        <v>0.0009742506484310083</v>
       </c>
       <c r="Q15">
-        <v>0.007297161351508334</v>
+        <v>0.0003089125040813994</v>
       </c>
       <c r="R15">
-        <v>0.08229738157998262</v>
+        <v>0.008982217657898126</v>
       </c>
       <c r="S15">
-        <v>0.01195091149181808</v>
+        <v>0.001652297837905493</v>
       </c>
       <c r="T15">
-        <v>0.08351499619338398</v>
+        <v>0.00506970202726985</v>
       </c>
       <c r="U15">
-        <v>0.01861419662774795</v>
+        <v>0.003010986222142269</v>
       </c>
       <c r="V15">
-        <v>0.02490387503589981</v>
+        <v>0.001539789467201369</v>
       </c>
       <c r="W15">
-        <v>0.005152193917769431</v>
+        <v>0.0006288097893689173</v>
       </c>
       <c r="X15">
-        <v>0.0368184682025211</v>
+        <v>0.001740662029465532</v>
       </c>
       <c r="Y15">
-        <v>0.01092897443296651</v>
+        <v>0.00217110766570657</v>
       </c>
       <c r="Z15">
-        <v>3.770089277785117</v>
+        <v>2.080817465051824</v>
       </c>
       <c r="AA15">
-        <v>0.3465121530472487</v>
+        <v>0.3462763733234836</v>
       </c>
       <c r="AB15">
-        <v>0.100589217120909</v>
+        <v>0.008197099525193841</v>
       </c>
       <c r="AC15">
-        <v>0.01745205486442951</v>
+        <v>0.004853943873697611</v>
       </c>
     </row>
     <row r="16">
@@ -1782,88 +1782,88 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.99335750581699</v>
+        <v>0.983800276676587</v>
       </c>
       <c r="C16">
-        <v>0.001110280571653551</v>
+        <v>0.001579645615000105</v>
       </c>
       <c r="D16">
-        <v>0.9899730551582056</v>
+        <v>0.9761054396888633</v>
       </c>
       <c r="E16">
-        <v>0.001659887660708658</v>
+        <v>0.002294206214657295</v>
       </c>
       <c r="F16">
-        <v>0.9958799068888505</v>
+        <v>0.9900728121548147</v>
       </c>
       <c r="G16">
-        <v>0.0006877077671356849</v>
+        <v>0.0009715314183051477</v>
       </c>
       <c r="H16">
-        <v>0.1157919446998024</v>
+        <v>0.1635720716500026</v>
       </c>
       <c r="I16">
-        <v>0.01713202523886006</v>
+        <v>0.02036437312137754</v>
       </c>
       <c r="J16">
-        <v>0.00853944846607909</v>
+        <v>0.02093315071152699</v>
       </c>
       <c r="K16">
-        <v>0.001421712329311906</v>
+        <v>0.002009434196460234</v>
       </c>
       <c r="L16">
-        <v>0.007435717283518019</v>
+        <v>0.0181471627631192</v>
       </c>
       <c r="M16">
-        <v>0.001233635600051623</v>
+        <v>0.001728446676617647</v>
       </c>
       <c r="N16">
-        <v>0.007481295515426618</v>
+        <v>0.01840924132479162</v>
       </c>
       <c r="O16">
-        <v>0.001248891652291973</v>
+        <v>0.001778775736370062</v>
       </c>
       <c r="P16">
-        <v>0.0008886441211891369</v>
+        <v>0.003073370652042368</v>
       </c>
       <c r="Q16">
-        <v>0.0002734260886384048</v>
+        <v>0.0006663683761355129</v>
       </c>
       <c r="R16">
-        <v>0.008598129792789627</v>
+        <v>0.02128111268107363</v>
       </c>
       <c r="S16">
-        <v>0.001441527833442053</v>
+        <v>0.002077292171539377</v>
       </c>
       <c r="T16">
-        <v>0.006923143680618762</v>
+        <v>0.01698071028256249</v>
       </c>
       <c r="U16">
-        <v>0.002635813056071557</v>
+        <v>0.003462708020067041</v>
       </c>
       <c r="V16">
-        <v>0.001843012517090527</v>
+        <v>0.003940102546125896</v>
       </c>
       <c r="W16">
-        <v>0.0005693519331749675</v>
+        <v>0.0008257049224428518</v>
       </c>
       <c r="X16">
-        <v>0.002586915664556421</v>
+        <v>0.006479068344233119</v>
       </c>
       <c r="Y16">
-        <v>0.001801188567841182</v>
+        <v>0.002396575388464315</v>
       </c>
       <c r="Z16">
-        <v>2.260488816466844</v>
+        <v>3.09651641155385</v>
       </c>
       <c r="AA16">
-        <v>0.3871230959850769</v>
+        <v>0.4632757583964096</v>
       </c>
       <c r="AB16">
-        <v>0.01118616826028611</v>
+        <v>0.02766868390035588</v>
       </c>
       <c r="AC16">
-        <v>0.004238761569422502</v>
+        <v>0.005568309909035437</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Convex_combination/Clustering/n10000/Summary_Statistics.xlsx
+++ b/Results/Convex_combination/Clustering/n10000/Summary_Statistics.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -482,20 +482,10 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Var_H_Fisher_mean</t>
+          <t>Var_C_Shannon_mean</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Var_H_Fisher_sd</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Var_C_Shannon_mean</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Var_C_Shannon_sd</t>
         </is>
@@ -526,10 +516,10 @@
         <v>0.002960776115189072</v>
       </c>
       <c r="H2">
-        <v>3.037134550891914</v>
+        <v>0.5863745911468858</v>
       </c>
       <c r="I2">
-        <v>0.09656957190226856</v>
+        <v>0.01441303943607622</v>
       </c>
       <c r="J2">
         <v>0.2174276617336838</v>
@@ -550,10 +540,10 @@
         <v>0.004829255319801952</v>
       </c>
       <c r="P2">
-        <v>0.7269919312034587</v>
+        <v>0.1403330022426851</v>
       </c>
       <c r="Q2">
-        <v>0.04249838541531036</v>
+        <v>0.007170835335683217</v>
       </c>
       <c r="R2">
         <v>0.273716523027738</v>
@@ -580,15 +570,9 @@
         <v>0.007151758209490461</v>
       </c>
       <c r="Z2">
-        <v>71.58674054706015</v>
+        <v>0.1370730671872683</v>
       </c>
       <c r="AA2">
-        <v>2.550641840998153</v>
-      </c>
-      <c r="AB2">
-        <v>0.1370730671872683</v>
-      </c>
-      <c r="AC2">
         <v>0.007618338032630846</v>
       </c>
     </row>
@@ -617,10 +601,10 @@
         <v>0.003323012834772537</v>
       </c>
       <c r="H3">
-        <v>2.472557651460757</v>
+        <v>0.5071435008915578</v>
       </c>
       <c r="I3">
-        <v>0.09937714437055475</v>
+        <v>0.01681441828922823</v>
       </c>
       <c r="J3">
         <v>0.1744451697251402</v>
@@ -641,10 +625,10 @@
         <v>0.005720481728166223</v>
       </c>
       <c r="P3">
-        <v>0.4472574660849187</v>
+        <v>0.09171265905920138</v>
       </c>
       <c r="Q3">
-        <v>0.03494907707891034</v>
+        <v>0.006528041297851415</v>
       </c>
       <c r="R3">
         <v>0.206706181076073</v>
@@ -671,15 +655,9 @@
         <v>0.005288581697565774</v>
       </c>
       <c r="Z3">
-        <v>66.81693736716169</v>
+        <v>0.1892955659618927</v>
       </c>
       <c r="AA3">
-        <v>2.943279553043202</v>
-      </c>
-      <c r="AB3">
-        <v>0.1892955659618927</v>
-      </c>
-      <c r="AC3">
         <v>0.007999320014956613</v>
       </c>
     </row>
@@ -708,10 +686,10 @@
         <v>0.0009846614002000187</v>
       </c>
       <c r="H4">
-        <v>0.2031243127751638</v>
+        <v>0.04960823137348938</v>
       </c>
       <c r="I4">
-        <v>0.02141757103589466</v>
+        <v>0.005133626331162862</v>
       </c>
       <c r="J4">
         <v>0.03016345706148782</v>
@@ -732,10 +710,10 @@
         <v>0.001825705600650306</v>
       </c>
       <c r="P4">
-        <v>0.005516020029920301</v>
+        <v>0.001346984908625248</v>
       </c>
       <c r="Q4">
-        <v>0.0009401233178717317</v>
+        <v>0.0002268438824444665</v>
       </c>
       <c r="R4">
         <v>0.03088580350349528</v>
@@ -762,15 +740,9 @@
         <v>0.002711079245648806</v>
       </c>
       <c r="Z4">
-        <v>3.741394705908122</v>
+        <v>0.03833144273664915</v>
       </c>
       <c r="AA4">
-        <v>0.4947423612864056</v>
-      </c>
-      <c r="AB4">
-        <v>0.03833144273664915</v>
-      </c>
-      <c r="AC4">
         <v>0.006284637671453579</v>
       </c>
     </row>
@@ -799,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.376743834386861</v>
+        <v>0.8016438184416944</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -823,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>3.274506204570922</v>
+        <v>0.4116501659025249</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -853,15 +825,9 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>-0.00840919224086285</v>
+        <v>0.0001907271167832054</v>
       </c>
       <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.0001907271167832054</v>
-      </c>
-      <c r="AC5">
         <v>0</v>
       </c>
     </row>
@@ -890,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3.628339195001781</v>
+        <v>0.5072798732912907</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -914,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.303504193108462</v>
+        <v>0.3220540452270046</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -944,15 +910,9 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>7.404718280581235</v>
+        <v>0.01652238002097946</v>
       </c>
       <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.01652238002097946</v>
-      </c>
-      <c r="AC6">
         <v>0</v>
       </c>
     </row>
@@ -981,10 +941,10 @@
         <v>0.009086712984963044</v>
       </c>
       <c r="H7">
-        <v>2.144800757908613</v>
+        <v>0.3950700503981212</v>
       </c>
       <c r="I7">
-        <v>0.09417060759548199</v>
+        <v>0.0118159547436874</v>
       </c>
       <c r="J7">
         <v>0.2716142016106999</v>
@@ -1005,10 +965,10 @@
         <v>0.003930538136860543</v>
       </c>
       <c r="P7">
-        <v>0.9899839104514545</v>
+        <v>0.1822843581202905</v>
       </c>
       <c r="Q7">
-        <v>0.07171567331836701</v>
+        <v>0.01067106210068897</v>
       </c>
       <c r="R7">
         <v>0.5275940313049715</v>
@@ -1035,15 +995,9 @@
         <v>0.02022855521123102</v>
       </c>
       <c r="Z7">
-        <v>15.14965353373947</v>
+        <v>0.007904853661870175</v>
       </c>
       <c r="AA7">
-        <v>0.9315230647283174</v>
-      </c>
-      <c r="AB7">
-        <v>0.007904853661870175</v>
-      </c>
-      <c r="AC7">
         <v>0.001643933327095412</v>
       </c>
     </row>
@@ -1072,10 +1026,10 @@
         <v>0.01767340456107068</v>
       </c>
       <c r="H8">
-        <v>1.606441176910535</v>
+        <v>0.3198904154452212</v>
       </c>
       <c r="I8">
-        <v>0.0210302517407413</v>
+        <v>0.003777617187336165</v>
       </c>
       <c r="J8">
         <v>0.2444301750717919</v>
@@ -1096,10 +1050,10 @@
         <v>0.004451530408409953</v>
       </c>
       <c r="P8">
-        <v>0.5102308509776134</v>
+        <v>0.1015828424796427</v>
       </c>
       <c r="Q8">
-        <v>0.0230018018409545</v>
+        <v>0.004063198959607921</v>
       </c>
       <c r="R8">
         <v>0.3634814067337032</v>
@@ -1126,15 +1080,9 @@
         <v>0.02191069998353674</v>
       </c>
       <c r="Z8">
-        <v>9.390087771045847</v>
+        <v>0.07408076265804241</v>
       </c>
       <c r="AA8">
-        <v>0.7485077404328102</v>
-      </c>
-      <c r="AB8">
-        <v>0.07408076265804241</v>
-      </c>
-      <c r="AC8">
         <v>0.009613239142752559</v>
       </c>
     </row>
@@ -1163,10 +1111,10 @@
         <v>0.01197802215213614</v>
       </c>
       <c r="H9">
-        <v>1.827386143027371</v>
+        <v>0.3671626315318049</v>
       </c>
       <c r="I9">
-        <v>0.07015224496650939</v>
+        <v>0.0121800089975681</v>
       </c>
       <c r="J9">
         <v>0.2171703245519144</v>
@@ -1187,10 +1135,10 @@
         <v>0.004784448249892042</v>
       </c>
       <c r="P9">
-        <v>0.4464106912083023</v>
+        <v>0.08970453603007866</v>
       </c>
       <c r="Q9">
-        <v>0.01028626623146859</v>
+        <v>0.001800966673684288</v>
       </c>
       <c r="R9">
         <v>0.2798838762342001</v>
@@ -1217,15 +1165,9 @@
         <v>0.03651525122365496</v>
       </c>
       <c r="Z9">
-        <v>18.04778700836314</v>
+        <v>0.0933670293782697</v>
       </c>
       <c r="AA9">
-        <v>2.571848492555791</v>
-      </c>
-      <c r="AB9">
-        <v>0.0933670293782697</v>
-      </c>
-      <c r="AC9">
         <v>0.006195017520366463</v>
       </c>
     </row>
@@ -1254,10 +1196,10 @@
         <v>0.002212694509758641</v>
       </c>
       <c r="H10">
-        <v>5.147584163317431</v>
+        <v>0.7587505487392028</v>
       </c>
       <c r="I10">
-        <v>0.08453764155103688</v>
+        <v>0.004952206566523335</v>
       </c>
       <c r="J10">
         <v>0.3187694963196284</v>
@@ -1278,10 +1220,10 @@
         <v>0.003825206015149443</v>
       </c>
       <c r="P10">
-        <v>2.235801900355239</v>
+        <v>0.3295164680149439</v>
       </c>
       <c r="Q10">
-        <v>0.06639150848013753</v>
+        <v>0.006686334353541795</v>
       </c>
       <c r="R10">
         <v>0.496965930382727</v>
@@ -1308,15 +1250,9 @@
         <v>0.003846864812893103</v>
       </c>
       <c r="Z10">
-        <v>59.05599396809212</v>
+        <v>0.02713106093417507</v>
       </c>
       <c r="AA10">
-        <v>4.42721178736164</v>
-      </c>
-      <c r="AB10">
-        <v>0.02713106093417507</v>
-      </c>
-      <c r="AC10">
         <v>0.003176159807762584</v>
       </c>
     </row>
@@ -1345,10 +1281,10 @@
         <v>0.003347474279025483</v>
       </c>
       <c r="H11">
-        <v>2.260917703194973</v>
+        <v>0.4741902321205454</v>
       </c>
       <c r="I11">
-        <v>0.09543149471498941</v>
+        <v>0.0167203446820265</v>
       </c>
       <c r="J11">
         <v>0.1438181179223706</v>
@@ -1369,10 +1305,10 @@
         <v>0.005752082886234918</v>
       </c>
       <c r="P11">
-        <v>0.3254313954759816</v>
+        <v>0.06823437946994765</v>
       </c>
       <c r="Q11">
-        <v>0.02842247172711878</v>
+        <v>0.005512659101328829</v>
       </c>
       <c r="R11">
         <v>0.1644246086440879</v>
@@ -1399,15 +1335,9 @@
         <v>0.005742547085555575</v>
       </c>
       <c r="Z11">
-        <v>59.80648199857379</v>
+        <v>0.1945974984051364</v>
       </c>
       <c r="AA11">
-        <v>2.860610542160025</v>
-      </c>
-      <c r="AB11">
-        <v>0.1945974984051364</v>
-      </c>
-      <c r="AC11">
         <v>0.009726707995719334</v>
       </c>
     </row>
@@ -1436,10 +1366,10 @@
         <v>0.003818144318990473</v>
       </c>
       <c r="H12">
-        <v>4.063535059222295</v>
+        <v>0.6727945772641016</v>
       </c>
       <c r="I12">
-        <v>0.1046545745111825</v>
+        <v>0.01014547409463873</v>
       </c>
       <c r="J12">
         <v>0.2759828013114681</v>
@@ -1460,10 +1390,10 @@
         <v>0.005537267549478905</v>
       </c>
       <c r="P12">
-        <v>1.379059688204052</v>
+        <v>0.2282724280574694</v>
       </c>
       <c r="Q12">
-        <v>0.06906509006607682</v>
+        <v>0.009003005657010787</v>
       </c>
       <c r="R12">
         <v>0.3881528121162313</v>
@@ -1490,15 +1420,9 @@
         <v>0.004356480793293855</v>
       </c>
       <c r="Z12">
-        <v>56.05313579146441</v>
+        <v>0.06456473210619906</v>
       </c>
       <c r="AA12">
-        <v>3.431749212952457</v>
-      </c>
-      <c r="AB12">
-        <v>0.06456473210619906</v>
-      </c>
-      <c r="AC12">
         <v>0.004800194512121427</v>
       </c>
     </row>
@@ -1527,10 +1451,10 @@
         <v>0.001581414779757471</v>
       </c>
       <c r="H13">
-        <v>0.3804630662594367</v>
+        <v>0.09077956798334938</v>
       </c>
       <c r="I13">
-        <v>0.03429580739577314</v>
+        <v>0.007747028120828057</v>
       </c>
       <c r="J13">
         <v>0.04715354148183693</v>
@@ -1551,10 +1475,10 @@
         <v>0.002846558597234428</v>
       </c>
       <c r="P13">
-        <v>0.01637499764835196</v>
+        <v>0.003905824927050442</v>
       </c>
       <c r="Q13">
-        <v>0.002610903270249857</v>
+        <v>0.000602826369495794</v>
       </c>
       <c r="R13">
         <v>0.04896906322399475</v>
@@ -1581,15 +1505,9 @@
         <v>0.003843806886159128</v>
       </c>
       <c r="Z13">
-        <v>7.141045142518886</v>
+        <v>0.05902475223378458</v>
       </c>
       <c r="AA13">
-        <v>0.7093497631197466</v>
-      </c>
-      <c r="AB13">
-        <v>0.05902475223378458</v>
-      </c>
-      <c r="AC13">
         <v>0.007921442429667021</v>
       </c>
     </row>
@@ -1618,10 +1536,10 @@
         <v>0.007886408169713267</v>
       </c>
       <c r="H14">
-        <v>0.4785425017924044</v>
+        <v>0.1103095114528522</v>
       </c>
       <c r="I14">
-        <v>0.04496966986284615</v>
+        <v>0.009696827116871936</v>
       </c>
       <c r="J14">
         <v>0.09847862021907149</v>
@@ -1642,10 +1560,10 @@
         <v>0.01027086223875231</v>
       </c>
       <c r="P14">
-        <v>0.04562249493605415</v>
+        <v>0.01050959019442824</v>
       </c>
       <c r="Q14">
-        <v>0.009957692874770392</v>
+        <v>0.002230636874572811</v>
       </c>
       <c r="R14">
         <v>0.1079387739909487</v>
@@ -1672,15 +1590,9 @@
         <v>0.01335293682986013</v>
       </c>
       <c r="Z14">
-        <v>4.249892116406888</v>
+        <v>0.125746752836536</v>
       </c>
       <c r="AA14">
-        <v>0.3344037868685192</v>
-      </c>
-      <c r="AB14">
-        <v>0.125746752836536</v>
-      </c>
-      <c r="AC14">
         <v>0.01449737096349169</v>
       </c>
     </row>
@@ -1709,10 +1621,10 @@
         <v>0.000800014161913692</v>
       </c>
       <c r="H15">
-        <v>0.1215958441116</v>
+        <v>0.02993993020026416</v>
       </c>
       <c r="I15">
-        <v>0.0173559219204826</v>
+        <v>0.004202398822864187</v>
       </c>
       <c r="J15">
         <v>0.008917920938243619</v>
@@ -1733,10 +1645,10 @@
         <v>0.001430391403872025</v>
       </c>
       <c r="P15">
-        <v>0.0009742506484310083</v>
+        <v>0.0002397703342740893</v>
       </c>
       <c r="Q15">
-        <v>0.0003089125040813994</v>
+        <v>7.532983073600791E-05</v>
       </c>
       <c r="R15">
         <v>0.008982217657898126</v>
@@ -1763,15 +1675,9 @@
         <v>0.00217110766570657</v>
       </c>
       <c r="Z15">
-        <v>2.080817465051824</v>
+        <v>0.008197099525193841</v>
       </c>
       <c r="AA15">
-        <v>0.3462763733234836</v>
-      </c>
-      <c r="AB15">
-        <v>0.008197099525193841</v>
-      </c>
-      <c r="AC15">
         <v>0.004853943873697611</v>
       </c>
     </row>
@@ -1800,10 +1706,10 @@
         <v>0.0009715314183051477</v>
       </c>
       <c r="H16">
-        <v>0.1635720716500026</v>
+        <v>0.04020871342811166</v>
       </c>
       <c r="I16">
-        <v>0.02036437312137754</v>
+        <v>0.004932398075667999</v>
       </c>
       <c r="J16">
         <v>0.02093315071152699</v>
@@ -1824,10 +1730,10 @@
         <v>0.001778775736370062</v>
       </c>
       <c r="P16">
-        <v>0.003073370652042368</v>
+        <v>0.0007553608095406789</v>
       </c>
       <c r="Q16">
-        <v>0.0006663683761355129</v>
+        <v>0.0001623771372645804</v>
       </c>
       <c r="R16">
         <v>0.02128111268107363</v>
@@ -1854,15 +1760,9 @@
         <v>0.002396575388464315</v>
       </c>
       <c r="Z16">
-        <v>3.09651641155385</v>
+        <v>0.02766868390035588</v>
       </c>
       <c r="AA16">
-        <v>0.4632757583964096</v>
-      </c>
-      <c r="AB16">
-        <v>0.02766868390035588</v>
-      </c>
-      <c r="AC16">
         <v>0.005568309909035437</v>
       </c>
     </row>
